--- a/0-出荷日計算/711-出荷日計算 -注通.xlsx
+++ b/0-出荷日計算/711-出荷日計算 -注通.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19800" windowHeight="14440" tabRatio="865" firstSheet="1"/>
+    <workbookView windowWidth="18350" windowHeight="17010" tabRatio="865" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="大阪 (祝日の希望到着日判断あり) (2)" sheetId="383" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="87">
   <si>
     <t>1列</t>
   </si>
@@ -305,73 +305,19 @@
     <t>沖縄</t>
   </si>
   <si>
-    <t>26O00525</t>
+    <t>作業</t>
   </si>
   <si>
-    <t>26O00526</t>
+    <t>大</t>
   </si>
   <si>
-    <t>26O00527</t>
+    <t>部品：業者持ち込み</t>
   </si>
   <si>
-    <t>海外</t>
+    <t>関東ｻｰﾋﾞｽｾﾝﾀｰへ</t>
   </si>
   <si>
-    <t>26O00528</t>
-  </si>
-  <si>
-    <t>26O00529</t>
-  </si>
-  <si>
-    <t>26O00530</t>
-  </si>
-  <si>
-    <t>26O00510</t>
-  </si>
-  <si>
-    <t>26O00511</t>
-  </si>
-  <si>
-    <t>26O00512</t>
-  </si>
-  <si>
-    <t>26O00513</t>
-  </si>
-  <si>
-    <t>26O00514</t>
-  </si>
-  <si>
-    <t>26O00515</t>
-  </si>
-  <si>
-    <t>26O00516</t>
-  </si>
-  <si>
-    <t>26T00499</t>
-  </si>
-  <si>
-    <t>26T00500</t>
-  </si>
-  <si>
-    <t>26T00501</t>
-  </si>
-  <si>
-    <t>26T00502</t>
-  </si>
-  <si>
-    <t>26T00503</t>
-  </si>
-  <si>
-    <t>26T00323</t>
-  </si>
-  <si>
-    <t>26T00322</t>
-  </si>
-  <si>
-    <t>26T00504</t>
-  </si>
-  <si>
-    <t>26T00505</t>
+    <t>千葉県</t>
   </si>
 </sst>
 </file>
@@ -1346,6 +1292,7 @@
       <color rgb="00E3A29F"/>
       <color rgb="00FF66FF"/>
       <color rgb="00FF0000"/>
+      <color rgb="00FFFF00"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2113,8 +2060,6 @@
       </c>
     </row>
     <row r="17" customHeight="1" spans="9:15">
-      <c r="I17"/>
-      <c r="J17" s="28"/>
       <c r="L17" s="35" t="e" cm="1">
         <f t="array" ref="L17">WORKDAY(M17,-VLOOKUP(J17,エリア!A:B,2,FALSE),_xlfn._xlws.FILTER(カレンダ!A:A,カレンダ!B:B="×"))</f>
         <v>#N/A</v>
@@ -2137,7 +2082,6 @@
     </row>
     <row r="19" customHeight="1" spans="9:15">
       <c r="I19"/>
-      <c r="J19" s="28"/>
       <c r="L19" s="35" t="e" cm="1">
         <f t="array" ref="L19">WORKDAY(M19,-VLOOKUP(J19,エリア!A:B,2,FALSE),_xlfn._xlws.FILTER(カレンダ!A:A,カレンダ!B:B="×"))</f>
         <v>#N/A</v>
@@ -2150,7 +2094,6 @@
     </row>
     <row r="20" customHeight="1" spans="9:15">
       <c r="I20"/>
-      <c r="J20" s="28"/>
       <c r="L20" s="35" t="e" cm="1">
         <f t="array" ref="L20">WORKDAY(M20,-VLOOKUP(J20,エリア!A:B,2,FALSE),_xlfn._xlws.FILTER(カレンダ!A:A,カレンダ!B:B="×"))</f>
         <v>#N/A</v>
@@ -2163,7 +2106,6 @@
     </row>
     <row r="21" customHeight="1" spans="9:15">
       <c r="I21"/>
-      <c r="J21" s="28"/>
       <c r="L21" s="35" t="e" cm="1">
         <f t="array" ref="L21">WORKDAY(M21,-VLOOKUP(J21,エリア!A:B,2,FALSE),_xlfn._xlws.FILTER(カレンダ!A:A,カレンダ!B:B="×"))</f>
         <v>#N/A</v>
@@ -2176,7 +2118,6 @@
     </row>
     <row r="22" customHeight="1" spans="9:15">
       <c r="I22"/>
-      <c r="J22" s="28"/>
       <c r="L22" s="35" t="e" cm="1">
         <f t="array" ref="L22">WORKDAY(M22,-VLOOKUP(J22,エリア!A:B,2,FALSE),_xlfn._xlws.FILTER(カレンダ!A:A,カレンダ!B:B="×"))</f>
         <v>#N/A</v>
@@ -2199,7 +2140,6 @@
     </row>
     <row r="24" customHeight="1" spans="9:15">
       <c r="I24"/>
-      <c r="J24" s="28"/>
       <c r="L24" s="35" t="e" cm="1">
         <f t="array" ref="L24">WORKDAY(M24,-VLOOKUP(J24,エリア!A:B,2,FALSE),_xlfn._xlws.FILTER(カレンダ!A:A,カレンダ!B:B="×"))</f>
         <v>#N/A</v>
@@ -2222,7 +2162,6 @@
     </row>
     <row r="26" customHeight="1" spans="9:15">
       <c r="I26"/>
-      <c r="J26" s="28"/>
       <c r="L26" s="35" t="e" cm="1">
         <f t="array" ref="L26">WORKDAY(M26,-VLOOKUP(J26,エリア!A:B,2,FALSE),_xlfn._xlws.FILTER(カレンダ!A:A,カレンダ!B:B="×"))</f>
         <v>#N/A</v>
@@ -14035,393 +13974,350 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="B1:F28"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="22" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="B1:I28"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="22" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.72727272727273" style="1"/>
     <col min="2" max="2" width="20.3636363636364" style="2" customWidth="1"/>
     <col min="3" max="4" width="8.72727272727273" style="2"/>
     <col min="5" max="6" width="20.1818181818182" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.72727272727273" style="1"/>
+    <col min="7" max="7" width="8.72727272727273" style="1"/>
+    <col min="8" max="8" width="19.3636363636364" style="1"/>
+    <col min="9" max="9" width="20.8181818181818" style="1"/>
+    <col min="10" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="2:6">
-      <c r="B1" s="4" t="s">
+    <row r="1" customHeight="1" spans="2:9">
+      <c r="B1" s="4"/>
+      <c r="C1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="E1" s="3">
-        <v>46237</v>
-      </c>
-      <c r="F1" s="3">
+        <v>31</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4">
+        <v>46236</v>
+      </c>
+      <c r="I1" s="4">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="2:9">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="3">
+        <v>32</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4">
         <v>46239</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="2:6">
-      <c r="B2" s="4" t="s">
+      <c r="I2" s="4">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="2:9">
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E3" s="3">
+        <v>33</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4">
+        <v>46253</v>
+      </c>
+      <c r="I3" s="4">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:9">
+      <c r="B4" s="4"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="3">
+        <v>34</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
+        <v>46259</v>
+      </c>
+      <c r="I4" s="4">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:9">
+      <c r="B5" s="4"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" customHeight="1" spans="2:9">
+      <c r="B6" s="4"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="3">
+        <v>535</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3">
-        <v>46254</v>
-      </c>
-      <c r="F2" s="3">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="2:6">
-      <c r="B3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F3" s="3">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="2:6">
-      <c r="B4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3">
-        <v>46280</v>
-      </c>
-      <c r="F4" s="3">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="2:6">
-      <c r="B5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3">
-        <v>46274</v>
-      </c>
-      <c r="F5" s="3">
-        <v>46279</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="2:6">
-      <c r="B6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3">
-        <v>46267</v>
-      </c>
-      <c r="F6" s="3">
-        <v>46268</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="2:6">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4">
+        <v>46289</v>
+      </c>
+      <c r="I6" s="4">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:9">
       <c r="B7" s="4"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3" t="e">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="2:6">
-      <c r="B8" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>78</v>
-      </c>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" customHeight="1" spans="2:9">
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="3">
-        <v>46260</v>
-      </c>
-      <c r="F8" s="3">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="2:6">
-      <c r="B9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" customHeight="1" spans="2:9">
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="E9" s="3">
-        <v>46290</v>
-      </c>
-      <c r="F9" s="3">
-        <v>46295</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="2:6">
-      <c r="B10" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="3"/>
+        <v>506</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4">
+        <v>46364</v>
+      </c>
+      <c r="I9" s="4">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:9">
+      <c r="B10" s="4"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="E10" s="3">
-        <v>46273</v>
-      </c>
-      <c r="F10" s="3">
+        <v>507</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4">
+        <v>46393</v>
+      </c>
+      <c r="I10" s="4">
+        <v>46395</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:9">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="3">
+        <v>508</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4">
+        <v>46238</v>
+      </c>
+      <c r="I11" s="4">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:9">
+      <c r="B12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="3">
+        <v>509</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4">
+        <v>46254</v>
+      </c>
+      <c r="I12" s="4">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:9">
+      <c r="B13" s="4"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I13" s="4">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="2:9">
+      <c r="B14" s="4"/>
+      <c r="C14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="3">
+        <v>510</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4">
+        <v>46274</v>
+      </c>
+      <c r="I14" s="4">
         <v>46276</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:6">
-      <c r="B11" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3">
-        <v>46259</v>
-      </c>
-      <c r="F11" s="3">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="2:6">
-      <c r="B12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3">
-        <v>46280</v>
-      </c>
-      <c r="F12" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="2:6">
-      <c r="B13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3">
-        <v>46282</v>
-      </c>
-      <c r="F13" s="3">
-        <v>46290</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="2:6">
-      <c r="B14" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3">
-        <v>46266</v>
-      </c>
-      <c r="F14" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="2:6">
+    <row r="15" customHeight="1" spans="2:9">
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="3" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="2:6">
-      <c r="B16" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>37</v>
-      </c>
+    </row>
+    <row r="16" customHeight="1" spans="2:9">
+      <c r="B16" s="4"/>
+      <c r="C16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="3">
-        <v>46268</v>
-      </c>
-      <c r="F16" s="3">
-        <v>46272</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="2:6">
+    </row>
+    <row r="17" customHeight="1" spans="2:4">
       <c r="B17" s="4"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
-      <c r="E17" s="3" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="2:6">
-      <c r="B18" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>48</v>
-      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:4">
+      <c r="B18" s="4"/>
+      <c r="C18" s="3"/>
       <c r="D18" s="3"/>
-      <c r="E18" s="3">
-        <v>46233</v>
-      </c>
-      <c r="F18" s="3">
-        <v>46237</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="2:6">
-      <c r="B19" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>37</v>
-      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:4">
+      <c r="B19" s="4"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
-      <c r="E19" s="3">
-        <v>46237</v>
-      </c>
-      <c r="F19" s="3">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="2:6">
-      <c r="B20" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>37</v>
-      </c>
+    </row>
+    <row r="20" customHeight="1" spans="2:4">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="3">
-        <v>46317</v>
-      </c>
-      <c r="F20" s="3">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="2:6">
-      <c r="B21" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>48</v>
-      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:4">
+      <c r="B21" s="4"/>
+      <c r="C21" s="3"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="3">
-        <v>46267</v>
-      </c>
-      <c r="F21" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="2:6">
+    </row>
+    <row r="22" customHeight="1" spans="2:4">
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="3" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="2:6">
-      <c r="B23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>39</v>
-      </c>
+    </row>
+    <row r="23" customHeight="1" spans="2:4">
+      <c r="B23" s="4"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="3">
-        <v>46253</v>
-      </c>
-      <c r="F23" s="3">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="2:6">
+    </row>
+    <row r="24" customHeight="1" spans="2:4">
       <c r="B24" s="4"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="3" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="2:6">
-      <c r="B25" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>40</v>
-      </c>
+    </row>
+    <row r="25" customHeight="1" spans="2:4">
+      <c r="B25" s="4"/>
+      <c r="C25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="3">
-        <v>46239</v>
-      </c>
-      <c r="F25" s="3">
-        <v>46241</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="2:6">
+    </row>
+    <row r="26" customHeight="1" spans="2:4">
       <c r="B26" s="4"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="3" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="2:6">
-      <c r="B27" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>50</v>
-      </c>
+    </row>
+    <row r="27" customHeight="1" spans="2:4">
+      <c r="B27" s="4"/>
+      <c r="C27" s="3"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="3">
-        <v>46275</v>
-      </c>
-      <c r="F27" s="3">
-        <v>46276</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="2:6">
-      <c r="B28" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>50</v>
-      </c>
+    </row>
+    <row r="28" customHeight="1" spans="2:4">
+      <c r="B28" s="4"/>
+      <c r="C28" s="3"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="3">
-        <v>46275</v>
-      </c>
-      <c r="F28" s="3">
-        <v>46276</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
